--- a/2024-09-20018D Source Data Ext. Fig. 7.xlsx
+++ b/2024-09-20018D Source Data Ext. Fig. 7.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\Source Data_Clean_KNIT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\Source Data_Clean_KNIT v3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A6CC44-9563-4FEE-8C15-0E504263F19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C022894-F266-4785-B607-CA0C6E1E0770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -696,13 +696,13 @@
         <v>0.76</v>
       </c>
       <c r="E4" s="9">
-        <v>71.7</v>
+        <v>73.3</v>
       </c>
       <c r="F4" s="9">
-        <v>74.900000000000006</v>
+        <v>74.3</v>
       </c>
       <c r="G4" s="9">
-        <v>72.900000000000006</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="3" t="s">

--- a/2024-09-20018D Source Data Ext. Fig. 7.xlsx
+++ b/2024-09-20018D Source Data Ext. Fig. 7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\Source Data_Clean_KNIT v3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\To be revised\Source data\Clean version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C022894-F266-4785-B607-CA0C6E1E0770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B97842-5A25-4C60-AAD4-522A5B154FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ext. Fig. 7a" sheetId="7" r:id="rId1"/>
@@ -19,17 +19,6 @@
     <sheet name="Ext. Fig. 7d" sheetId="13" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -69,9 +58,6 @@
     <t>nCas9</t>
   </si>
   <si>
-    <t>Ext. Fig. 7b (top)</t>
-  </si>
-  <si>
     <t>Ext. Fig. 7c (bottom)</t>
   </si>
   <si>
@@ -95,6 +81,10 @@
   </si>
   <si>
     <t>KE1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ext. Fig. 7b</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -241,7 +231,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -271,6 +261,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -578,43 +569,43 @@
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="7"/>
       <c r="I2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13" t="s">
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
       <c r="Q2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="R2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13" t="s">
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="5" t="s">
@@ -664,13 +655,13 @@
         <v>0</v>
       </c>
       <c r="R3" s="10">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S3" s="10">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="T3" s="10">
-        <v>2.2000000000000002</v>
+        <v>2.19</v>
       </c>
       <c r="U3" s="10">
         <v>19.7</v>
@@ -709,13 +700,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="10">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="K4" s="10">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L4" s="10">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="M4" s="10">
         <v>49.5</v>
@@ -733,10 +724,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="S4" s="10">
-        <v>2.1</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="T4" s="10">
-        <v>2.1</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="U4" s="10">
         <v>24</v>
@@ -816,16 +807,16 @@
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="9">
-        <v>0.28999999999999998</v>
+        <v>0.45</v>
       </c>
       <c r="C6" s="9">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="9">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="E6" s="9">
         <v>44.2</v>
@@ -838,7 +829,7 @@
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" s="10">
         <v>0.27</v>
@@ -859,7 +850,7 @@
         <v>31.5</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R6" s="10">
         <v>0.19</v>
@@ -882,7 +873,7 @@
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="9">
         <v>0.6</v>
@@ -904,16 +895,16 @@
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J7" s="10">
-        <v>3.2000000000000001E-2</v>
+        <v>0.15</v>
       </c>
       <c r="K7" s="10">
-        <v>0.22</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L7" s="10">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
       <c r="M7" s="10">
         <v>38.299999999999997</v>
@@ -925,7 +916,7 @@
         <v>42.3</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R7" s="10">
         <v>0.24</v>
@@ -972,62 +963,62 @@
   <sheetData>
     <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="15" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="18"/>
       <c r="I2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="16"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="15" t="s">
+      <c r="K2" s="17"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="16"/>
-      <c r="O2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="18"/>
       <c r="Q2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="R2" s="15" t="s">
+      <c r="R2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="S2" s="16"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="15" t="s">
+      <c r="S2" s="17"/>
+      <c r="T2" s="18"/>
+      <c r="U2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="V2" s="16"/>
-      <c r="W2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="18"/>
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="10">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="C3" s="10">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="D3" s="10">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="E3" s="10">
         <v>37.799999999999997</v>
@@ -1089,10 +1080,10 @@
         <v>1.6</v>
       </c>
       <c r="C4" s="10">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="D4" s="10">
-        <v>1.1000000000000001</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="E4" s="10">
         <v>91.7</v>
@@ -1107,13 +1098,13 @@
         <v>9</v>
       </c>
       <c r="J4" s="10">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="K4" s="10">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="L4" s="10">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="M4" s="10">
         <v>66.7</v>
@@ -1134,7 +1125,7 @@
         <v>0.79</v>
       </c>
       <c r="T4" s="10">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="U4" s="10">
         <v>22.6</v>
@@ -1151,10 +1142,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="10">
-        <v>1.1000000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="C5" s="10">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="D5" s="10">
         <v>0.53</v>
@@ -1172,13 +1163,13 @@
         <v>10</v>
       </c>
       <c r="J5" s="10">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="K5" s="10">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="L5" s="10">
-        <v>9.5000000000000001E-2</v>
+        <v>0.35</v>
       </c>
       <c r="M5" s="10">
         <v>10.4</v>
@@ -1213,16 +1204,16 @@
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="10">
-        <v>2.2999999999999998</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="C6" s="10">
-        <v>2.2999999999999998</v>
+        <v>2.25</v>
       </c>
       <c r="D6" s="10">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="E6" s="10">
         <v>54.1</v>
@@ -1234,7 +1225,7 @@
         <v>58.2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" s="10">
         <v>0.79</v>
@@ -1255,7 +1246,7 @@
         <v>57.4</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R6" s="10">
         <v>0.62</v>
@@ -1278,7 +1269,7 @@
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="10">
         <v>1.1000000000000001</v>
@@ -1299,7 +1290,7 @@
         <v>92.6</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J7" s="10">
         <v>0.44</v>
@@ -1320,16 +1311,16 @@
         <v>85.36</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R7" s="10">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="S7" s="10">
         <v>0.67</v>
       </c>
       <c r="T7" s="10">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="U7" s="10">
         <v>52.5</v>
@@ -1367,49 +1358,49 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="I2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13" t="s">
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="I2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10">
-        <v>1.8</v>
-      </c>
-      <c r="C3" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="D3" s="10">
-        <v>1.6</v>
+      <c r="B3" s="13">
+        <v>1.83</v>
+      </c>
+      <c r="C3" s="13">
+        <v>0.33</v>
+      </c>
+      <c r="D3" s="13">
+        <v>1.57</v>
       </c>
       <c r="E3" s="10">
         <v>10.3</v>
@@ -1424,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="10">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="K3" s="10">
         <v>0.53</v>
@@ -1444,16 +1435,16 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="C4" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="D4" s="10">
-        <v>1.4</v>
+        <v>14</v>
+      </c>
+      <c r="B4" s="13">
+        <v>1.62</v>
+      </c>
+      <c r="C4" s="13">
+        <v>1.58</v>
+      </c>
+      <c r="D4" s="13">
+        <v>1.44</v>
       </c>
       <c r="E4" s="10">
         <v>16.3</v>
@@ -1465,7 +1456,7 @@
         <v>17.899999999999999</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J4" s="10">
         <v>0.84</v>
@@ -1490,14 +1481,14 @@
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="D5" s="10">
-        <v>1.7</v>
+      <c r="B5" s="13">
+        <v>1.47</v>
+      </c>
+      <c r="C5" s="13">
+        <v>1.66</v>
+      </c>
+      <c r="D5" s="13">
+        <v>1.75</v>
       </c>
       <c r="E5" s="10">
         <v>6.5</v>
@@ -1512,13 +1503,13 @@
         <v>10</v>
       </c>
       <c r="J5" s="10">
-        <v>1.1000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="K5" s="10">
         <v>0.76</v>
       </c>
       <c r="L5" s="10">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M5" s="10">
         <v>4.0999999999999996</v>
@@ -1532,15 +1523,15 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="12">
+        <v>18</v>
+      </c>
+      <c r="B6" s="13">
         <v>1.7</v>
       </c>
-      <c r="C6" s="12">
-        <v>0.4</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="C6" s="13">
+        <v>0.41</v>
+      </c>
+      <c r="D6" s="13">
         <v>0.96</v>
       </c>
       <c r="E6" s="12">
@@ -1553,7 +1544,7 @@
         <v>27.5</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" s="10">
         <v>0.49</v>
@@ -1576,16 +1567,16 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1.6</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0.94</v>
+        <v>17</v>
+      </c>
+      <c r="B7" s="13">
+        <v>1.56</v>
+      </c>
+      <c r="C7" s="13">
+        <v>1.63</v>
+      </c>
+      <c r="D7" s="13">
+        <v>0.93</v>
       </c>
       <c r="E7" s="10">
         <v>30.9</v>
@@ -1597,16 +1588,16 @@
         <v>20.5</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J7" s="10">
-        <v>0.81</v>
+        <v>0.72</v>
       </c>
       <c r="K7" s="10">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="L7" s="10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="M7" s="10">
         <v>24.4</v>
@@ -1642,31 +1633,31 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2"/>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="10">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="C3" s="10">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="D3" s="10">
         <v>3.8</v>
@@ -1692,7 +1683,7 @@
         <v>0.82</v>
       </c>
       <c r="D4" s="10">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="E4" s="10">
         <v>36.5</v>
@@ -1712,16 +1703,16 @@
         <v>1.5</v>
       </c>
       <c r="C5" s="10">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="D5" s="10">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="E5" s="10">
-        <v>7</v>
+        <v>6.99</v>
       </c>
       <c r="F5" s="10">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="G5" s="10">
         <v>3.6</v>
@@ -1729,16 +1720,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="10">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="C6" s="10">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="D6" s="10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="E6" s="10">
         <v>30.2</v>
@@ -1752,16 +1743,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="10">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="C7" s="10">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="D7" s="10">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="E7" s="10">
         <v>38.700000000000003</v>

--- a/2024-09-20018D Source Data Ext. Fig. 7.xlsx
+++ b/2024-09-20018D Source Data Ext. Fig. 7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\To be revised\Source data\Clean version\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Source Data_Proof\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B97842-5A25-4C60-AAD4-522A5B154FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14EACD7B-6053-488B-A479-0CDF4C977625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1063,10 +1063,10 @@
         <v>0.83</v>
       </c>
       <c r="U3" s="10">
-        <v>5.9</v>
+        <v>5.87</v>
       </c>
       <c r="V3" s="10">
-        <v>6.9</v>
+        <v>6.94</v>
       </c>
       <c r="W3" s="10">
         <v>13</v>
@@ -1193,13 +1193,13 @@
         <v>0.71</v>
       </c>
       <c r="U5" s="10">
-        <v>5.9</v>
+        <v>5.94</v>
       </c>
       <c r="V5" s="10">
-        <v>5.9</v>
+        <v>5.88</v>
       </c>
       <c r="W5" s="10">
-        <v>7.1</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="6" spans="1:23">
